--- a/ML-Entrees/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T09:43:36+00:00</t>
+    <t>2026-04-08T13:03:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T13:03:38+00:00</t>
+    <t>2026-04-08T14:07:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:07:03+00:00</t>
+    <t>2026-04-09T12:24:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T12:24:05+00:00</t>
+    <t>2026-04-13T08:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T08:58:24+00:00</t>
+    <t>2026-04-13T09:04:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:04:52+00:00</t>
+    <t>2026-04-14T07:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="134">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T07:59:58+00:00</t>
+    <t>2026-04-16T07:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Rencontre</t>
+    <t>Entrée Rencontre</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -108,7 +108,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Base</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-entry</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -250,46 +250,177 @@
     <t>Base</t>
   </si>
   <si>
-    <t>fr-lm-encounter.identifiant</t>
+    <t>fr-lm-encounter.header</t>
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base
+</t>
+  </si>
+  <si>
+    <t>Métadonnées de base</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.header.subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-usager
+</t>
+  </si>
+  <si>
+    <t>Patient/subject information</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.subject</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.header.identifier</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier
 </t>
   </si>
   <si>
-    <t>Identifiant de l'entrée</t>
-  </si>
-  <si>
-    <t>fr-lm-encounter.typeRencontre</t>
+    <t>Identifiant de l’entrée</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.identifier</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.header.author[x]</t>
+  </si>
+  <si>
+    <t>author[x] peut correspondre soit à un professionnel, soit à une organisation, soit à un système.</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.header.author[x].authorProfessional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>L'auteur est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.header.performer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
+</t>
+  </si>
+  <si>
+    <t>Exécutant (performer)</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.performer</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.header.participant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-participant-corps
+</t>
+  </si>
+  <si>
+    <t>Participant</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.header.informant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informateur
+</t>
+  </si>
+  <si>
+    <t>Informateur</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.informant</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.header.date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Date/Heure de création par l'auteur</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.date</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.header.source</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.source</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.header.langue</t>
+  </si>
+  <si>
+    <t>'fr-FR' pour français métropolitain (la casse des caractères doit être respectée)
+La partie en minuscules indique le code de la langue utilisée (ISO-639-1)
+La partie en majuscules indique le code pays (ISO-3166)</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.langue</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.typeRencontre</t>
+  </si>
+  <si>
     <t>Type de rencontre</t>
   </si>
   <si>
-    <t>fr-lm-encounter.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Description narrative</t>
-  </si>
-  <si>
     <t>fr-lm-encounter.dateRencontre</t>
   </si>
   <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
     <t>Date de la rencontre</t>
   </si>
   <si>
@@ -297,52 +428,6 @@
   </si>
   <si>
     <t>Confirmation attendue</t>
-  </si>
-  <si>
-    <t>fr-lm-encounter.executant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
-</t>
-  </si>
-  <si>
-    <t>Exécutant</t>
-  </si>
-  <si>
-    <t>fr-lm-encounter.auteur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-auteur
-</t>
-  </si>
-  <si>
-    <t>Auteur</t>
-  </si>
-  <si>
-    <t>fr-lm-encounter.informateur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informateur
-</t>
-  </si>
-  <si>
-    <t>Informateur</t>
-  </si>
-  <si>
-    <t>fr-lm-encounter.participant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-participant-corps
-</t>
-  </si>
-  <si>
-    <t>Lieu d'exécution (PersonneStructure)</t>
-  </si>
-  <si>
-    <t>fr-lm-encounter.autreParticipant</t>
-  </si>
-  <si>
-    <t>Participant (utilisable dans le corps du document uniquement)</t>
   </si>
 </sst>
 </file>
@@ -644,11 +729,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ12"/>
+  <dimension ref="A1:AJ18"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="31.77734375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="31.77734375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="42.828125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -657,7 +742,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="73.859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="79.609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -678,7 +763,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="31.77734375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="38.97265625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -910,7 +995,7 @@
         <v>79</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>73</v>
@@ -979,13 +1064,13 @@
         <v>73</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>73</v>
@@ -996,10 +1081,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1022,13 +1107,13 @@
         <v>73</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1079,7 +1164,7 @@
         <v>73</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>79</v>
@@ -1096,10 +1181,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1110,7 +1195,7 @@
         <v>74</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>73</v>
@@ -1122,13 +1207,13 @@
         <v>73</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1179,13 +1264,13 @@
         <v>73</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>73</v>
@@ -1196,10 +1281,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1210,7 +1295,7 @@
         <v>74</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>73</v>
@@ -1222,13 +1307,13 @@
         <v>73</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1279,13 +1364,13 @@
         <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>73</v>
@@ -1296,10 +1381,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1310,7 +1395,7 @@
         <v>74</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>73</v>
@@ -1322,13 +1407,13 @@
         <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1379,13 +1464,13 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>73</v>
@@ -1396,10 +1481,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1422,13 +1507,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1479,7 +1564,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1496,10 +1581,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1522,13 +1607,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1579,7 +1664,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -1596,10 +1681,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1622,13 +1707,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1679,7 +1764,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1696,10 +1781,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1710,7 +1795,7 @@
         <v>74</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>73</v>
@@ -1722,13 +1807,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1779,13 +1864,13 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>73</v>
@@ -1796,10 +1881,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1810,7 +1895,7 @@
         <v>74</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>73</v>
@@ -1822,13 +1907,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1879,18 +1964,618 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G13" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="AI12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
+      <c r="H13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K13" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q13" s="2"/>
+      <c r="R13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF13" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K14" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q14" s="2"/>
+      <c r="R14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K15" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q15" s="2"/>
+      <c r="R15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K16" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q16" s="2"/>
+      <c r="R16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q17" s="2"/>
+      <c r="R17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q18" s="2"/>
+      <c r="R18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF18" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="148">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:11:11+00:00</t>
+    <t>2026-04-24T08:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -304,7 +304,7 @@
     <t>fr-lm-encounter.header.author[x].authorProfessional</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
 </t>
   </si>
   <si>
@@ -317,6 +317,10 @@
     <t>fr-lm-encounter.header.author[x].authorOrganisation</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation
+</t>
+  </si>
+  <si>
     <t>L'auteur est une organisation</t>
   </si>
   <si>
@@ -326,7 +330,7 @@
     <t>fr-lm-encounter.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-device
 </t>
   </si>
   <si>
@@ -336,36 +340,59 @@
     <t>fr-lm-entry.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t>fr-lm-encounter.header.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
-</t>
+    <t>fr-lm-encounter.header.performer[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.performer</t>
-  </si>
-  <si>
-    <t>fr-lm-encounter.header.participant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-participant-corps
-</t>
+    <t>fr-lm-entry.header.performer[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.header.participant[x]</t>
   </si>
   <si>
     <t>Participant</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.participant</t>
+    <t>fr-lm-entry.header.participant[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>Le participant est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>Le participant est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.header.participant[x].participantDevice</t>
+  </si>
+  <si>
+    <t>Le participant est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantDevice</t>
   </si>
   <si>
     <t>fr-lm-encounter.header.informant</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informateur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informant
 </t>
   </si>
   <si>
@@ -388,11 +415,26 @@
     <t>fr-lm-entry.header.date</t>
   </si>
   <si>
-    <t>fr-lm-encounter.header.source</t>
+    <t>fr-lm-encounter.header.status</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
+  </si>
+  <si>
+    <t>Statut de l'acte</t>
+  </si>
+  <si>
+    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.status</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.header.source</t>
   </si>
   <si>
     <t>Source</t>
@@ -729,11 +771,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ18"/>
+  <dimension ref="A1:AJ22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="42.828125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="42.828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.5390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="49.5390625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -742,7 +784,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="79.609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="73.875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -756,14 +798,14 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="47.0546875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.58203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.97265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="45.68359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1507,13 +1549,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1564,7 +1606,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1581,10 +1623,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1607,13 +1649,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1664,7 +1706,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -1681,10 +1723,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1707,13 +1749,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1764,7 +1806,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1781,10 +1823,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1807,7 +1849,7 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>111</v>
@@ -1907,13 +1949,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L12" t="s" s="2">
-        <v>115</v>
-      </c>
       <c r="M12" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1964,7 +2006,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -1981,10 +2023,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -1995,7 +2037,7 @@
         <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>73</v>
@@ -2007,13 +2049,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2064,13 +2106,13 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>73</v>
@@ -2081,10 +2123,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2095,7 +2137,7 @@
         <v>74</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>73</v>
@@ -2107,13 +2149,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2164,13 +2206,13 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>73</v>
@@ -2181,10 +2223,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2195,7 +2237,7 @@
         <v>74</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>73</v>
@@ -2207,13 +2249,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2264,13 +2306,13 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>73</v>
@@ -2281,10 +2323,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2292,7 +2334,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>79</v>
@@ -2307,13 +2349,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2364,10 +2406,10 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>79</v>
@@ -2392,7 +2434,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>79</v>
@@ -2407,13 +2449,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2443,10 +2485,10 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2464,10 +2506,10 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>79</v>
@@ -2481,10 +2523,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2507,13 +2549,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2564,7 +2606,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2576,6 +2618,406 @@
         <v>73</v>
       </c>
       <c r="AJ18" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="F19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K19" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q19" s="2"/>
+      <c r="R19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q22" s="2"/>
+      <c r="R22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:31:26+00:00</t>
+    <t>2026-04-24T12:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T12:30:57+00:00</t>
+    <t>2026-04-24T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
